--- a/backend/scheme.xlsx
+++ b/backend/scheme.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/theis/Documents/Dock folder/Repos/borrow-system/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178FA041-4FD3-E44B-9078-9ECFCAA8B915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1E0B56-988D-B248-AE3D-F780B184C861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4340" yWindow="-28180" windowWidth="51200" windowHeight="24540" activeTab="2" xr2:uid="{C8FDF089-DA29-D94D-9C59-AF6D7D2004E6}"/>
+    <workbookView xWindow="-4340" yWindow="-28180" windowWidth="51200" windowHeight="24540" activeTab="1" xr2:uid="{C8FDF089-DA29-D94D-9C59-AF6D7D2004E6}"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>id</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>last_borrowed_person</t>
+  </si>
+  <si>
+    <t>note</t>
   </si>
 </sst>
 </file>
@@ -532,7 +535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39CFD817-29FE-BE49-8BF8-3EB8866768B2}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
@@ -546,7 +549,7 @@
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,6 +582,9 @@
       </c>
       <c r="K1" t="s">
         <v>17</v>
+      </c>
+      <c r="L1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
